--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2022_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2022_valparaiso.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:41</t>
+    <t xml:space="preserve">2026-09-09 20:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2022_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2022_valparaiso.xlsx
@@ -24,111 +24,111 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Fernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Pascua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Algarrobo</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Larga</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
-    <t xml:space="preserve">Casablanca</t>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Tabo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
     <t xml:space="preserve">Catemu</t>
   </si>
   <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Quisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Tabo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hijuelas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Pascua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Fernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
   </si>
   <si>
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Olmué</t>
   </si>
   <si>
-    <t xml:space="preserve">Panquehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilpué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Felipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
-    <t xml:space="preserve">Zapallar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:45</t>
+    <t xml:space="preserve">2026-09-18 10:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="4">
@@ -566,7 +566,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="8">
@@ -598,7 +598,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.91</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="9">
@@ -606,7 +606,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.18</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="10">
@@ -614,7 +614,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="11">
@@ -622,7 +622,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="12">
@@ -630,7 +630,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3.22</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="13">
@@ -638,7 +638,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="14">
@@ -646,7 +646,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.94</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="15">
@@ -654,7 +654,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.75</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="16">
@@ -662,7 +662,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.09</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="17">
@@ -670,7 +670,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.51</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="18">
@@ -678,7 +678,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.89</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="19">
@@ -686,7 +686,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="20">
@@ -694,7 +694,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2.84</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.79</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="22">
@@ -710,7 +710,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.87</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="23">
@@ -718,7 +718,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>3.9</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="24">
@@ -726,7 +726,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="25">
@@ -734,7 +734,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3.31</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="26">
@@ -742,7 +742,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="27">
@@ -750,7 +750,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4.02</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +758,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2.59</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="29">
@@ -766,7 +766,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2.28</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="30">
@@ -774,7 +774,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="31">
@@ -782,7 +782,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="32">
@@ -798,7 +798,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1.65</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="34">
@@ -806,7 +806,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="35">
@@ -814,7 +814,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="36">
@@ -822,7 +822,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1.78</v>
+        <v>2.95</v>
       </c>
     </row>
   </sheetData>
